--- a/data_member_statcal.xlsx
+++ b/data_member_statcal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MODUL STATCAL\WEBSITE STATCAL\Member of STATCAL\testing 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9264CC93-F163-4A52-810B-6FD1A92BE0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441DE31C-311A-44BD-B1CE-FBC645B0DF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>Location</t>
   </si>
@@ -114,23 +114,47 @@
     <t>August 10, 2026</t>
   </si>
   <si>
-    <t>August 10, 2027</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
     <t>Occupation</t>
+  </si>
+  <si>
+    <t>Rodyah Widyarini</t>
+  </si>
+  <si>
+    <t>Master's Degree</t>
+  </si>
+  <si>
+    <t>Universitas Primagraha</t>
+  </si>
+  <si>
+    <t>Serang</t>
+  </si>
+  <si>
+    <t>August 10, 2031</t>
+  </si>
+  <si>
+    <t>August 11, 2031</t>
+  </si>
+  <si>
+    <t>August 11, 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -441,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
@@ -473,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -511,10 +535,10 @@
         <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -540,10 +564,10 @@
         <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -569,10 +593,10 @@
         <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -598,13 +622,43 @@
         <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>20260005</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>